--- a/data/golden/서울_시각정답_보강_초벌.xlsx
+++ b/data/golden/서울_시각정답_보강_초벌.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E019 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E019 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>E019 | 확신도medium</t>
+          <t>E019 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>E023 | 확신도medium</t>
+          <t>E023 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>E025 | 확신도medium</t>
+          <t>E025 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>E027 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E027 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>E027 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E027 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>E027 | 확신도medium</t>
+          <t>E027 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>E027 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E027 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>E027 | 확신도medium</t>
+          <t>E027 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>E027 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E027 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>E028 | 확신도medium</t>
+          <t>E028 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>E028 | 확신도medium</t>
+          <t>E028 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>E031 | 확신도medium</t>
+          <t>E031 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>E031 | 확신도medium</t>
+          <t>E031 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -4558,9 +4558,12 @@
           <t>84</t>
         </is>
       </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>E031 | 확신도medium</t>
+          <t>E031 | 확신도medium | 재검증:판독불가→채점제외 | 서울시 전체(적색) 2013 라벨을 확대 판독해도 '25.4'/'26.4' 중간 자릿수 판별 불가(스캔 흐림). 본문 '10년 전 대비 3.3㎞</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4611,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>E031 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E031 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5257,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E035 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5305,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E035 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5353,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E035 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5401,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium</t>
+          <t>E035 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5449,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E035 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5497,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium</t>
+          <t>E035 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5528,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>9.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5544,7 +5547,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium</t>
+          <t xml:space="preserve">E035 | 확신도medium | 재검증:교정(값=7.1) | 평균선 라벨을 확대 판독한 결과 '9.7일'은 주황색(열대야일수 계열색), '7.1일'은 적색(폭염일수 계열색)으로 인쇄됨. 폭염일수 100년 </t>
         </is>
       </c>
     </row>
@@ -5575,7 +5578,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>7.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5594,7 +5597,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>E035 | 확신도medium</t>
+          <t>E035 | 확신도medium | 재검증:교정(값=9.7) | 위와 동일 근거: 열대야일수 100년 평균은 주황색 라벨 '9.7일'. 초벌의 7.1은 폭염 값과 뒤바뀜</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5847,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5897,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5947,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5997,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6047,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6097,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6147,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6197,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6247,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6297,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6347,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6397,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6447,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6497,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6547,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6597,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6647,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6692,9 +6695,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 일최다강수량 91~00년 라벨 '16X.8' — X가 2/3 구분 불가(162.8/163.8 모두 막대높이 정합). 스캔 해상도 한계</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6750,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6792,9 +6798,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K131" t="n">
+        <v>1</v>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 일최다강수량 11~20년 라벨 '12X.9' — X가 5/6 구분 불가(125.9/126.9). 막대높이로도 판별 불가</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6853,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6892,9 +6901,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 강수강도 31~40년 라벨 '15.X' — X가 6/8 구분 불가. 본문 평균 16.6mm/일 검산도 15.6/15.8 둘 다 허용</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -6994,7 +7006,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7056,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7092,9 +7104,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 강수강도 71~80년 라벨이 추세선과 겹쳐 소수점 자리 판독 불가(15.5 기재값 부정도 확인도 불가)</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7159,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E037 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7209,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7259,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7309,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7359,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7392,9 +7407,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 최대무강수 31~40년 라벨 '18.X' — 확대 시 6/8 구분 불가(여러 배율에서 판독 결과가 엇갈림)</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7462,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7512,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7562,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7612,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7662,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7712,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -7742,9 +7760,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 최대무강수 01~10년 라벨 '19.X' — 8/9 구분 불가</t>
         </is>
       </c>
     </row>
@@ -7792,9 +7813,12 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>E037 | 확신도medium</t>
+          <t>E037 | 확신도medium | 재검증:판독불가→채점제외 | 최대무강수 11~20년 라벨 '22.X' — 6/8 구분 불가(확대 렌더는 22.8에 가깝게 보이나 열화 6도 동일하게 보임, 단정 불가)</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10268,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E055 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10318,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10368,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10418,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10468,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10518,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E055 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10568,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E055 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10618,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10668,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10718,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>E055 | 확신도medium</t>
+          <t>E055 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11266,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>E060 | 확신도medium</t>
+          <t>E060 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11314,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>E060 | 확신도medium</t>
+          <t>E060 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11362,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>E060 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E060 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13519,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>E067 | 확신도medium</t>
+          <t>E067 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13540,7 +13564,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>E067 | 확신도medium</t>
+          <t>E067 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13609,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>E067 | 확신도medium</t>
+          <t>E067 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13657,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>E067 | 확신도medium</t>
+          <t>E067 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13705,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>E067 | 확신도medium</t>
+          <t>E067 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13753,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13777,7 +13801,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13849,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13873,7 +13897,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13945,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -13969,7 +13993,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14041,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14089,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14137,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E068 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14185,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E068 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14233,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E068 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14281,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14329,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14353,7 +14377,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14425,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14473,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14521,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14545,7 +14569,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14617,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14665,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium</t>
+          <t>E068 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14713,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>E068 | 확신도medium | 텍스트레이어값존재</t>
+          <t>E068 | 확신도medium | 텍스트레이어값존재 | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15457,13 +15481,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>총계(순배출량)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15499,13 +15521,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>총계(순배출량)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2021</t>
@@ -15641,13 +15661,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>총계</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15673,7 +15691,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15683,13 +15701,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>가정</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15715,7 +15731,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15725,13 +15741,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>상업</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15757,7 +15771,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15767,13 +15781,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>수송</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15799,7 +15811,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15809,13 +15821,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>폐기물</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15841,7 +15851,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15851,13 +15861,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>공공</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2005</t>
@@ -15883,7 +15891,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15893,13 +15901,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>총계</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2021</t>
@@ -15925,7 +15931,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15935,13 +15941,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>상업</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2021</t>
@@ -15967,7 +15971,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -15977,13 +15981,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>가정</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2021</t>
@@ -16009,7 +16011,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -16019,13 +16021,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>수송</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2021</t>
@@ -16051,7 +16051,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -16061,13 +16061,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>폐기물</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2021</t>
@@ -16093,7 +16091,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -16103,13 +16101,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>공공</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>2021</t>
@@ -16135,7 +16131,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>E045 | 확신도medium</t>
+          <t>E045 | 확신도medium | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -16145,13 +16141,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>폐기물</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>2005</t>
@@ -16187,13 +16181,11 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>폐기물</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>2021</t>
@@ -16329,7 +16321,6 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>폐기물</t>
@@ -16375,7 +16366,6 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>폐기물</t>
@@ -16421,7 +16411,6 @@
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>폐기물</t>
@@ -17199,7 +17188,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>E015 | 추가필드:{"감축률": 40, "단위": "천톤CO2eq"}</t>
+          <t>E015 | 추가필드:{"감축률": 40, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17237,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>E015 | 추가필드:{"감축률": 70, "단위": "천톤CO2eq"}</t>
+          <t>E015 | 추가필드:{"감축률": 70, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17283,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>E015 | 추가필드:{"감축률": 100, "단위": "천톤CO2eq"}</t>
+          <t>E015 | 추가필드:{"감축률": 100, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17323,6 +17312,9 @@
       <c r="G5" t="n">
         <v>2030</v>
       </c>
+      <c r="I5" t="n">
+        <v>15425</v>
+      </c>
       <c r="J5" t="n">
         <v>31530</v>
       </c>
@@ -17338,7 +17330,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>E079 | 텍스트레이어값존재 | 추가필드:{"감축률": 40, "단위": "천톤CO2eq"}</t>
+          <t>E079 | 텍스트레이어값존재 | 추가필드:{"감축률": 40, "단위": "천톤CO2eq"} | 재검증:보완(목표감축량=15425) | 기재값 전부 원문 일치([그림 5-1] '2005년 대비 40% 감축, 2030년 목표 배출량 31,530천톤CO2eq', 본문 52,342천톤</t>
         </is>
       </c>
     </row>
@@ -17367,6 +17359,9 @@
       <c r="G6" t="n">
         <v>2033</v>
       </c>
+      <c r="I6" t="n">
+        <v>21670</v>
+      </c>
       <c r="J6" t="n">
         <v>25671</v>
       </c>
@@ -17382,7 +17377,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>E079 | 텍스트레이어값존재 | 추가필드:{"감축률": 51, "단위": "천톤CO2eq"}</t>
+          <t>E079 | 텍스트레이어값존재 | 추가필드:{"감축률": 51, "단위": "천톤CO2eq"} | 재검증:보완(목표감축량=21670) | 기재값 전부 원문 일치('2005년 대비 51% 감축, 2033년 목표 배출량 25,671천톤CO2eq'). 목표감축량 본문 명시: '2033년</t>
         </is>
       </c>
     </row>
@@ -17420,7 +17415,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>E079 | 추가필드:{"감축률": 70, "단위": "%"}</t>
+          <t>E079 | 추가필드:{"감축률": 70, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17458,7 +17453,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>E079 | 추가필드:{"감축률": 100, "단위": "%"}</t>
+          <t>E079 | 추가필드:{"감축률": 100, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17505,7 +17500,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>E080 | 추가필드:{"감축률": 51, "단위": "천톤CO2eq"}</t>
+          <t>E080 | 추가필드:{"감축률": 51, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17548,7 +17543,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>E080 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"}</t>
+          <t>E080 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17591,7 +17586,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>E080 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"}</t>
+          <t>E080 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17629,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>E080 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"}</t>
+          <t>E080 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17654,6 +17649,11 @@
           <t>관리권한</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
       <c r="E13" t="n">
         <v>2018</v>
       </c>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>E081 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"}</t>
+          <t>E081 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"} | 재검증:보완(부문=전체) | p185 그림 5-3 워터폴: '관리권한 내 2018 배출량 46,107' → '2030 목표 배출량 28,660' 라벨 확인, 값 전부 일치.</t>
         </is>
       </c>
     </row>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>E081 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"}</t>
+          <t>E081 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>E081 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"}</t>
+          <t>E081 | 텍스트레이어값존재 | 추가필드:{"감축률": null, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>E082 | 2033 BAU 47,341(막대 라벨). 폭포수차트: 양끝 막대=BAU/목표배출량, 중간 막대=부문별 감축량 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 2033 BAU 47,341(막대 라벨). 폭포수차트: 양끝 막대=BAU/목표배출량, 중간 막대=부문별 감축량 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>E082 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18065,7 +18065,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E082 | 텍스트레이어값존재 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>E083 | 텍스트레이어값존재 | 감축률은 BAU 대비(화살표 라벨 '18% 감축'), 화살표 도착점=목표배출량, 막대 상단 라벨=감축량 | 추가필드:{"감축률": 18, "단위": "천톤CO2eq"}</t>
+          <t>E083 | 텍스트레이어값존재 | 감축률은 BAU 대비(화살표 라벨 '18% 감축'), 화살표 도착점=목표배출량, 막대 상단 라벨=감축량 | 추가필드:{"감축률": 18, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>E083 | 텍스트레이어값존재 | 감축률은 BAU 대비(화살표 라벨 '25% 감축') | 추가필드:{"감축률": 25, "단위": "천톤CO2eq"}</t>
+          <t>E083 | 텍스트레이어값존재 | 감축률은 BAU 대비(화살표 라벨 '25% 감축') | 추가필드:{"감축률": 25, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18203,7 +18203,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>E084 | 확신도medium | 감축률은 BAU 대비(화살표 라벨 '30% 감축') | 추가필드:{"감축률": 30, "단위": "천톤CO2eq"}</t>
+          <t>E084 | 확신도medium | 감축률은 BAU 대비(화살표 라벨 '30% 감축') | 추가필드:{"감축률": 30, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>E084 | 확신도medium | 2033 감축량 라벨 인쇄 흐림: 3,383/3,283 판독 모호(확대 판독 3,383). 본문 로드맵 계획기간 누계는 3,285천톤으로 상이하므로 검증 필요 | 추가필드:{"감축률": 45, "단위": "천톤CO2eq"}</t>
+          <t>E084 | 확신도medium | 2033 감축량 라벨 인쇄 흐림: 3,383/3,283 판독 모호(확대 판독 3,383). 본문 로드맵 계획기간 누계는 3,285천톤으로 상이하므로 검증 필요 | 추가필드:{"감축률": 45, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>E085 | 확신도medium | 감축률은 BAU 대비(화살표 라벨 '9% 감축'). 2030 감축량 라벨 인쇄 흐림: 338/336 판독 모호 | 추가필드:{"감축률": 9, "단위": "천톤CO2eq"}</t>
+          <t>E085 | 확신도medium | 감축률은 BAU 대비(화살표 라벨 '9% 감축'). 2030 감축량 라벨 인쇄 흐림: 338/336 판독 모호 | 추가필드:{"감축률": 9, "단위": "천톤CO2eq"} | 재검증:교정(목표감축량=338) | p193 본문 '338천 톤' 명시(차트 라벨 흐림은 본문으로 해소)</t>
         </is>
       </c>
     </row>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>E085 | 확신도medium | 감축률은 BAU 대비(화살표 라벨 '10% 감축') | 추가필드:{"감축률": 10, "단위": "천톤CO2eq"}</t>
+          <t>E085 | 확신도medium | 감축률은 BAU 대비(화살표 라벨 '10% 감축') | 추가필드:{"감축률": 10, "단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>E086 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E086 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>E086 | 추가필드:{"단위": "천톤CO2eq"}</t>
+          <t>E086 | 추가필드:{"단위": "천톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>E087 | 추가필드:{"단위": "톤CO2eq"}</t>
+          <t>E087 | 추가필드:{"단위": "톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>E087 | 추가필드:{"단위": "톤CO2eq"}</t>
+          <t>E087 | 추가필드:{"단위": "톤CO2eq"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링(부문 비중) | 추가필드:{"값": 77, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링(부문 비중) | 추가필드:{"값": 77, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 그림 8-1 내부 링 | 추가필드:{"값": 12, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 그림 8-1 내부 링 | 추가필드:{"값": 12, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링 | 추가필드:{"값": 8, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링 | 추가필드:{"값": 8, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링 | 추가필드:{"값": 1, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링 | 추가필드:{"값": 1, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링 | 추가필드:{"값": 1, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 내부 링 | 추가필드:{"값": 1, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19562,7 +19562,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링(세부사업 비중) | 추가필드:{"값": 39, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링(세부사업 비중) | 추가필드:{"값": 39, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19599,7 +19599,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 그림 8-1 외부 링 | 추가필드:{"값": 36, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 그림 8-1 외부 링 | 추가필드:{"값": 36, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링 | 추가필드:{"값": 9, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링 | 추가필드:{"값": 9, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링 | 추가필드:{"값": 4, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링 | 추가필드:{"값": 4, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19710,7 +19710,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링 | 추가필드:{"값": 1, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-1 외부 링 | 추가필드:{"값": 1, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링(분야 비중) | 추가필드:{"값": 45, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링(분야 비중) | 추가필드:{"값": 45, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링 | 추가필드:{"값": 39, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링 | 추가필드:{"값": 39, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링 | 추가필드:{"값": 10, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링 | 추가필드:{"값": 10, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19858,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링, 라벨 일부 흐림 | 추가필드:{"값": 4, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링, 라벨 일부 흐림 | 추가필드:{"값": 4, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19895,7 +19895,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링 | 추가필드:{"값": 2, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 내부 링 | 추가필드:{"값": 2, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 외부 링(세부사업 비중) | 추가필드:{"값": 38, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 외부 링(세부사업 비중) | 추가필드:{"값": 38, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 외부 링 | 추가필드:{"값": 14, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 외부 링 | 추가필드:{"값": 14, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 그림 8-2 외부 링 | 추가필드:{"값": 13, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 그림 8-2 외부 링 | 추가필드:{"값": 13, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 그림 8-2 외부 링, 라벨 '기타 폭우대비12%' 흐림 | 추가필드:{"값": 12, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 그림 8-2 외부 링, 라벨 '기타 폭우대비12%' 흐림 | 추가필드:{"값": 12, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 외부 링 | 추가필드:{"값": 7, "단위": "%"}</t>
+          <t>E180 | 확신도medium | 텍스트레이어값존재 | 그림 8-2 외부 링 | 추가필드:{"값": 7, "단위": "%"} | 재검증:확정</t>
         </is>
       </c>
     </row>
